--- a/data/sports/rainbow_six/research.xlsx
+++ b/data/sports/rainbow_six/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ50" headerRowCount="1">
-  <autoFilter ref="A1:DQ50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ51" headerRowCount="1">
+  <autoFilter ref="A1:DQ51"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$50)</f>
+        <f>COUNTA('Picks'!$A$2:$A$51)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$50,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$51,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$50,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$50,"settled",'Picks'!$V$2:$V$50,"win")+COUNTIFS('Picks'!$U$2:$U$50,"settled",'Picks'!$V$2:$V$50,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")+COUNTIFS('Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$50,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$51,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$50,"&gt;0",'Picks'!$V$2:$V$50,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$50,"&gt;0",'Picks'!$V$2:$V$50,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$50,"&gt;0",'Picks'!$V$2:$V$50,"win")/(COUNTIFS('Picks'!$BX$2:$BX$50,"&gt;0",'Picks'!$V$2:$V$50,"win")+COUNTIFS('Picks'!$BX$2:$BX$50,"&gt;0",'Picks'!$V$2:$V$50,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")/(COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")+COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$50)/SUM('Picks'!$BX$2:$BX$50),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$51)/SUM('Picks'!$BX$2:$BX$51),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$50)</f>
+        <f>SUM('Picks'!$BY$2:$BY$51)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$50,"&lt;&gt;",'Picks'!$AB$2:$AB$50),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$51,"&lt;&gt;",'Picks'!$AB$2:$AB$51),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$50,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$50,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$51,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$50,'Picks'!$AM$2:$AM$50,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$51,'Picks'!$AM$2:$AM$51,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$50,$A14,'Picks'!$U$2:$U$50,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$50,$A14,'Picks'!$U$2:$U$50,"settled",'Picks'!$V$2:$V$50,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$50,$A14,'Picks'!$U$2:$U$50,"settled",'Picks'!$V$2:$V$50,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$50,'Picks'!$H$2:$H$50,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$50,'Picks'!$H$2:$H$50,$A14,'Picks'!$U$2:$U$50,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$50,$A15,'Picks'!$U$2:$U$50,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$50,$A15,'Picks'!$U$2:$U$50,"settled",'Picks'!$V$2:$V$50,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$50,$A15,'Picks'!$U$2:$U$50,"settled",'Picks'!$V$2:$V$50,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$50,'Picks'!$H$2:$H$50,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$50,'Picks'!$H$2:$H$50,$A15,'Picks'!$U$2:$U$50,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$50,$A16,'Picks'!$U$2:$U$50,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$50,$A16,'Picks'!$U$2:$U$50,"settled",'Picks'!$V$2:$V$50,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$50,$A16,'Picks'!$U$2:$U$50,"settled",'Picks'!$V$2:$V$50,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$50,'Picks'!$H$2:$H$50,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$50,'Picks'!$H$2:$H$50,$A16,'Picks'!$U$2:$U$50,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ50"/>
+  <dimension ref="A1:DQ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17446,6 +17446,327 @@
         </is>
       </c>
     </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>fd9136262c164b11</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T10:51:13.499333Z</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>144058</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>RAINBOW_SIX</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>Geekay Esports</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J51" s="25" t="n"/>
+      <c r="K51" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M51" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N51" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O51" s="28" t="n">
+        <v>0.54393</v>
+      </c>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="28" t="n">
+        <v>-0.0857</v>
+      </c>
+      <c r="R51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U51" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V51" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W51" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="25" t="n"/>
+      <c r="Z51" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA51" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB51" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC51" s="30" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AD51" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:02:52.165431Z</t>
+        </is>
+      </c>
+      <c r="AE51" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-r6-shi-ge-2026-10-06).</t>
+        </is>
+      </c>
+      <c r="AF51" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG51" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH51" s="24" t="n"/>
+      <c r="AI51" s="31" t="n"/>
+      <c r="AJ51" s="31" t="n"/>
+      <c r="AK51" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL51" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM51" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN51" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO51" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP51" s="24" t="inlineStr">
+        <is>
+          <t>Geekay Esports</t>
+        </is>
+      </c>
+      <c r="AQ51" s="24" t="inlineStr">
+        <is>
+          <t>Geekay Esports</t>
+        </is>
+      </c>
+      <c r="AR51" s="24" t="inlineStr">
+        <is>
+          <t>Geekay Esports</t>
+        </is>
+      </c>
+      <c r="AS51" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AT51" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AU51" s="24" t="inlineStr">
+        <is>
+          <t>Shifters</t>
+        </is>
+      </c>
+      <c r="AV51" s="24" t="n"/>
+      <c r="AW51" s="24" t="n"/>
+      <c r="AX51" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY51" s="24" t="n"/>
+      <c r="AZ51" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA51" s="24" t="inlineStr">
+        <is>
+          <t>9858f060c2a168107585edc8a721ca47c237812d7c1532146f3176089ebd00c8</t>
+        </is>
+      </c>
+      <c r="BB51" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC51" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD51" s="24" t="inlineStr">
+        <is>
+          <t>9858f060c2a168107585edc8a721ca47c237812d7c1532146f3176089ebd00c8</t>
+        </is>
+      </c>
+      <c r="BE51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG51" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH51" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T10:50:53.274144Z</t>
+        </is>
+      </c>
+      <c r="BI51" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ51" s="25" t="n"/>
+      <c r="BK51" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL51" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM51" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN51" s="28" t="n"/>
+      <c r="BO51" s="28" t="n"/>
+      <c r="BP51" s="25" t="n"/>
+      <c r="BQ51" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR51" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BS51" s="28" t="n"/>
+      <c r="BT51" s="28" t="n"/>
+      <c r="BU51" s="25" t="n"/>
+      <c r="BV51" s="29" t="n"/>
+      <c r="BW51" s="24" t="n"/>
+      <c r="BX51" s="30" t="n"/>
+      <c r="BY51" s="27" t="n"/>
+      <c r="BZ51" s="24" t="n"/>
+      <c r="CA51" s="31" t="n"/>
+      <c r="CB51" s="24" t="n"/>
+      <c r="CC51" s="24" t="n"/>
+      <c r="CD51" s="24" t="n"/>
+      <c r="CE51" s="24" t="n"/>
+      <c r="CF51" s="24" t="n"/>
+      <c r="CG51" s="24" t="n"/>
+      <c r="CH51" s="24" t="n"/>
+      <c r="CI51" s="24" t="n"/>
+      <c r="CJ51" s="24" t="n"/>
+      <c r="CK51" s="24" t="n"/>
+      <c r="CL51" s="24" t="n"/>
+      <c r="CM51" s="24" t="n"/>
+      <c r="CN51" s="24" t="n"/>
+      <c r="CO51" s="24" t="n"/>
+      <c r="CP51" s="24" t="n"/>
+      <c r="CQ51" s="24" t="n"/>
+      <c r="CR51" s="24" t="n"/>
+      <c r="CS51" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT51" s="24" t="n"/>
+      <c r="CU51" s="24" t="n"/>
+      <c r="CV51" s="24" t="n"/>
+      <c r="CW51" s="24" t="n"/>
+      <c r="CX51" s="24" t="n"/>
+      <c r="CY51" s="24" t="n"/>
+      <c r="CZ51" s="24" t="n"/>
+      <c r="DA51" s="24" t="n"/>
+      <c r="DB51" s="24" t="n"/>
+      <c r="DC51" s="24" t="n"/>
+      <c r="DD51" s="24" t="n"/>
+      <c r="DE51" s="24" t="n"/>
+      <c r="DF51" s="24" t="n"/>
+      <c r="DG51" s="24" t="n"/>
+      <c r="DH51" s="24" t="n"/>
+      <c r="DI51" s="24" t="n"/>
+      <c r="DJ51" s="24" t="n"/>
+      <c r="DK51" s="24" t="n"/>
+      <c r="DL51" s="24" t="n"/>
+      <c r="DM51" s="24" t="n"/>
+      <c r="DN51" s="24" t="n"/>
+      <c r="DO51" s="24" t="n"/>
+      <c r="DP51" s="24" t="n"/>
+      <c r="DQ51" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "9858f060c2a168107585edc8a721ca47c237812d7c1532146f3176089ebd00c8", "away_team": "Geekay Esports", "event_id": "144058", "event_start_utc": "2026-10-06T16:00:00Z", "features": {"away_elo": 1642.27105, "away_history_count": 61, "home_elo": 1566.086413, "home_history_count": 111}, "historical_source_observation_times_verified": false, "home_team": "Shifters", "inference_inputs": {"book_state": {"games_played": {"bo3:7:19340": 61, "bo3:7:19716": 111}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 32.0, "last_match_utc": {"bo3:7:19340": "2026-10-05T16:00:00Z", "bo3:7:19716": "2026-09-30T20:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.1370995612441656, "platt_slope": 0.763965360686399, "ratings": {"bo3:7:19340": 1642.27105, "bo3:7:19716": 1566.086413}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T10:50:53.103147+00:00", "team_ids": ["bo3:7:19716", "bo3:7:19340"]}, "market_type": "moneyline", "model_version": "rainbow_six-tiered-elo-v6", "observed_at_utc": "2026-10-06T10:50:53.103147+00:00", "probabilities": {"away": 0.54393, "home": 0.45607}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "35d45af2f9634daaecd155a5a9eb97f4a828a10292a99d3c614db99047ab3902", "sport": "RAINBOW_SIX"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/sports/rainbow_six/research.xlsx
+++ b/data/sports/rainbow_six/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ51" headerRowCount="1">
-  <autoFilter ref="A1:DQ51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ56" headerRowCount="1">
+  <autoFilter ref="A1:DQ56"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$51)</f>
+        <f>COUNTA('Picks'!$A$2:$A$56)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$51,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$56,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$51,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$56,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")+COUNTIFS('Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"win")+COUNTIFS('Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$51,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$56,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$56,"&gt;0",'Picks'!$V$2:$V$56,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$56,"&gt;0",'Picks'!$V$2:$V$56,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")/(COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")+COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$56,"&gt;0",'Picks'!$V$2:$V$56,"win")/(COUNTIFS('Picks'!$BX$2:$BX$56,"&gt;0",'Picks'!$V$2:$V$56,"win")+COUNTIFS('Picks'!$BX$2:$BX$56,"&gt;0",'Picks'!$V$2:$V$56,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$51)/SUM('Picks'!$BX$2:$BX$51),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$56)/SUM('Picks'!$BX$2:$BX$56),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$51)</f>
+        <f>SUM('Picks'!$BY$2:$BY$56)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$51,"&lt;&gt;",'Picks'!$AB$2:$AB$51),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$56,"&lt;&gt;",'Picks'!$AB$2:$AB$56),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$51,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$51,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$56,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$56,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$51,'Picks'!$AM$2:$AM$51,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$56,'Picks'!$AM$2:$AM$56,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$56,$A14,'Picks'!$U$2:$U$56,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$56,$A14,'Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$56,$A14,'Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$56,'Picks'!$H$2:$H$56,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$56,'Picks'!$H$2:$H$56,$A14,'Picks'!$U$2:$U$56,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$56,$A15,'Picks'!$U$2:$U$56,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$56,$A15,'Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$56,$A15,'Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$56,'Picks'!$H$2:$H$56,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$56,'Picks'!$H$2:$H$56,$A15,'Picks'!$U$2:$U$56,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$56,$A16,'Picks'!$U$2:$U$56,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$56,$A16,'Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$56,$A16,'Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$56,'Picks'!$H$2:$H$56,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$56,'Picks'!$H$2:$H$56,$A16,'Picks'!$U$2:$U$56,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ51"/>
+  <dimension ref="A1:DQ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17767,6 +17767,1611 @@
         </is>
       </c>
     </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>e4b1ea99a8b1487f</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:28:03.287087Z</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-08T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>143744</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>RAINBOW_SIX</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>DarkZero Esports</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J52" s="25" t="n"/>
+      <c r="K52" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M52" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N52" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O52" s="28" t="n">
+        <v>0.562983</v>
+      </c>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="28" t="n">
+        <v>-0.127419</v>
+      </c>
+      <c r="R52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U52" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V52" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="25" t="n"/>
+      <c r="Z52" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="AA52" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB52" s="28" t="n">
+        <v>0.009598000000000001</v>
+      </c>
+      <c r="AC52" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD52" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:37:12.112830Z</t>
+        </is>
+      </c>
+      <c r="AE52" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-r6-c9-dz-2026-10-08).</t>
+        </is>
+      </c>
+      <c r="AF52" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG52" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH52" s="24" t="n"/>
+      <c r="AI52" s="31" t="n"/>
+      <c r="AJ52" s="31" t="n"/>
+      <c r="AK52" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL52" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM52" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN52" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO52" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP52" s="24" t="inlineStr">
+        <is>
+          <t>DarkZero Esports</t>
+        </is>
+      </c>
+      <c r="AQ52" s="24" t="inlineStr">
+        <is>
+          <t>DarkZero Esports</t>
+        </is>
+      </c>
+      <c r="AR52" s="24" t="inlineStr">
+        <is>
+          <t>DarkZero Esports</t>
+        </is>
+      </c>
+      <c r="AS52" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AT52" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AU52" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AV52" s="24" t="n"/>
+      <c r="AW52" s="24" t="n"/>
+      <c r="AX52" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY52" s="24" t="n"/>
+      <c r="AZ52" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA52" s="24" t="inlineStr">
+        <is>
+          <t>6ba5d15b40a8ae0fc6edef9d2ee0f3d04150e80e420234231fec1c3c345f7a8f</t>
+        </is>
+      </c>
+      <c r="BB52" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC52" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD52" s="24" t="inlineStr">
+        <is>
+          <t>6ba5d15b40a8ae0fc6edef9d2ee0f3d04150e80e420234231fec1c3c345f7a8f</t>
+        </is>
+      </c>
+      <c r="BE52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG52" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH52" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:21.740280Z</t>
+        </is>
+      </c>
+      <c r="BI52" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ52" s="25" t="n"/>
+      <c r="BK52" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL52" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM52" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN52" s="28" t="n"/>
+      <c r="BO52" s="28" t="n"/>
+      <c r="BP52" s="25" t="n"/>
+      <c r="BQ52" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BR52" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BS52" s="28" t="n"/>
+      <c r="BT52" s="28" t="n"/>
+      <c r="BU52" s="25" t="n"/>
+      <c r="BV52" s="29" t="n"/>
+      <c r="BW52" s="24" t="n"/>
+      <c r="BX52" s="30" t="n"/>
+      <c r="BY52" s="27" t="n"/>
+      <c r="BZ52" s="24" t="n"/>
+      <c r="CA52" s="31" t="n"/>
+      <c r="CB52" s="24" t="n"/>
+      <c r="CC52" s="24" t="n"/>
+      <c r="CD52" s="24" t="n"/>
+      <c r="CE52" s="24" t="n"/>
+      <c r="CF52" s="24" t="n"/>
+      <c r="CG52" s="24" t="n"/>
+      <c r="CH52" s="24" t="n"/>
+      <c r="CI52" s="24" t="n"/>
+      <c r="CJ52" s="24" t="n"/>
+      <c r="CK52" s="24" t="n"/>
+      <c r="CL52" s="24" t="n"/>
+      <c r="CM52" s="24" t="n"/>
+      <c r="CN52" s="24" t="n"/>
+      <c r="CO52" s="24" t="n"/>
+      <c r="CP52" s="24" t="n"/>
+      <c r="CQ52" s="24" t="n"/>
+      <c r="CR52" s="24" t="n"/>
+      <c r="CS52" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT52" s="24" t="n"/>
+      <c r="CU52" s="24" t="n"/>
+      <c r="CV52" s="24" t="n"/>
+      <c r="CW52" s="24" t="n"/>
+      <c r="CX52" s="24" t="n"/>
+      <c r="CY52" s="24" t="n"/>
+      <c r="CZ52" s="24" t="n"/>
+      <c r="DA52" s="24" t="n"/>
+      <c r="DB52" s="24" t="n"/>
+      <c r="DC52" s="24" t="n"/>
+      <c r="DD52" s="24" t="n"/>
+      <c r="DE52" s="24" t="n"/>
+      <c r="DF52" s="24" t="n"/>
+      <c r="DG52" s="24" t="n"/>
+      <c r="DH52" s="24" t="n"/>
+      <c r="DI52" s="24" t="n"/>
+      <c r="DJ52" s="24" t="n"/>
+      <c r="DK52" s="24" t="n"/>
+      <c r="DL52" s="24" t="n"/>
+      <c r="DM52" s="24" t="n"/>
+      <c r="DN52" s="24" t="n"/>
+      <c r="DO52" s="24" t="n"/>
+      <c r="DP52" s="24" t="n"/>
+      <c r="DQ52" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "6ba5d15b40a8ae0fc6edef9d2ee0f3d04150e80e420234231fec1c3c345f7a8f", "away_team": "DarkZero Esports", "event_id": "143744", "event_start_utc": "2026-10-08T15:00:00Z", "features": {"away_elo": 1735.504181, "away_history_count": 127, "home_elo": 1632.634987, "home_history_count": 52}, "historical_source_observation_times_verified": false, "home_team": "Cloud9", "inference_inputs": {"book_state": {"games_played": {"bo3:7:19685": 52, "bo3:7:19729": 127}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 32.0, "last_match_utc": {"bo3:7:19685": "2026-10-02T20:00:00Z", "bo3:7:19729": "2026-10-02T22:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.1361313041024407, "platt_slope": 0.7681778963758318, "ratings": {"bo3:7:19685": 1632.634987, "bo3:7:19729": 1735.504181}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T22:27:21.600823+00:00", "team_ids": ["bo3:7:19685", "bo3:7:19729"]}, "market_type": "moneyline", "model_version": "rainbow_six-tiered-elo-v6", "observed_at_utc": "2026-10-07T22:27:21.600823+00:00", "probabilities": {"away": 0.562983, "home": 0.437017}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "a907813121397f018911f9a2d1e1a43c18c1bbed9d24a772b97263e43b204cc0", "sport": "RAINBOW_SIX"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>9aad4741ff074e21</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:28:03.287087Z</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>144060</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>RAINBOW_SIX</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion</t>
+        </is>
+      </c>
+      <c r="H53" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J53" s="25" t="n"/>
+      <c r="K53" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L53" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M53" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N53" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O53" s="28" t="n">
+        <v>0.608032</v>
+      </c>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="28" t="n">
+        <v>-0.091668</v>
+      </c>
+      <c r="R53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U53" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V53" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W53" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="25" t="n"/>
+      <c r="Z53" s="26" t="n">
+        <v>-400</v>
+      </c>
+      <c r="AA53" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB53" s="28" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="AC53" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD53" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:37:13.110910Z</t>
+        </is>
+      </c>
+      <c r="AE53" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-r6-sr-100t-2026-10-08).</t>
+        </is>
+      </c>
+      <c r="AF53" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG53" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH53" s="24" t="n"/>
+      <c r="AI53" s="31" t="n"/>
+      <c r="AJ53" s="31" t="n"/>
+      <c r="AK53" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL53" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM53" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN53" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO53" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP53" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AQ53" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AR53" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AS53" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion</t>
+        </is>
+      </c>
+      <c r="AT53" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion</t>
+        </is>
+      </c>
+      <c r="AU53" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion</t>
+        </is>
+      </c>
+      <c r="AV53" s="24" t="n"/>
+      <c r="AW53" s="24" t="n"/>
+      <c r="AX53" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY53" s="24" t="n"/>
+      <c r="AZ53" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA53" s="24" t="inlineStr">
+        <is>
+          <t>6ba5d15b40a8ae0fc6edef9d2ee0f3d04150e80e420234231fec1c3c345f7a8f</t>
+        </is>
+      </c>
+      <c r="BB53" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC53" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD53" s="24" t="inlineStr">
+        <is>
+          <t>6ba5d15b40a8ae0fc6edef9d2ee0f3d04150e80e420234231fec1c3c345f7a8f</t>
+        </is>
+      </c>
+      <c r="BE53" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF53" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG53" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH53" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:42.181627Z</t>
+        </is>
+      </c>
+      <c r="BI53" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ53" s="25" t="n"/>
+      <c r="BK53" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL53" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM53" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN53" s="28" t="n"/>
+      <c r="BO53" s="28" t="n"/>
+      <c r="BP53" s="25" t="n"/>
+      <c r="BQ53" s="27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BR53" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BS53" s="28" t="n"/>
+      <c r="BT53" s="28" t="n"/>
+      <c r="BU53" s="25" t="n"/>
+      <c r="BV53" s="29" t="n"/>
+      <c r="BW53" s="24" t="n"/>
+      <c r="BX53" s="30" t="n"/>
+      <c r="BY53" s="27" t="n"/>
+      <c r="BZ53" s="24" t="n"/>
+      <c r="CA53" s="31" t="n"/>
+      <c r="CB53" s="24" t="n"/>
+      <c r="CC53" s="24" t="n"/>
+      <c r="CD53" s="24" t="n"/>
+      <c r="CE53" s="24" t="n"/>
+      <c r="CF53" s="24" t="n"/>
+      <c r="CG53" s="24" t="n"/>
+      <c r="CH53" s="24" t="n"/>
+      <c r="CI53" s="24" t="n"/>
+      <c r="CJ53" s="24" t="n"/>
+      <c r="CK53" s="24" t="n"/>
+      <c r="CL53" s="24" t="n"/>
+      <c r="CM53" s="24" t="n"/>
+      <c r="CN53" s="24" t="n"/>
+      <c r="CO53" s="24" t="n"/>
+      <c r="CP53" s="24" t="n"/>
+      <c r="CQ53" s="24" t="n"/>
+      <c r="CR53" s="24" t="n"/>
+      <c r="CS53" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT53" s="24" t="n"/>
+      <c r="CU53" s="24" t="n"/>
+      <c r="CV53" s="24" t="n"/>
+      <c r="CW53" s="24" t="n"/>
+      <c r="CX53" s="24" t="n"/>
+      <c r="CY53" s="24" t="n"/>
+      <c r="CZ53" s="24" t="n"/>
+      <c r="DA53" s="24" t="n"/>
+      <c r="DB53" s="24" t="n"/>
+      <c r="DC53" s="24" t="n"/>
+      <c r="DD53" s="24" t="n"/>
+      <c r="DE53" s="24" t="n"/>
+      <c r="DF53" s="24" t="n"/>
+      <c r="DG53" s="24" t="n"/>
+      <c r="DH53" s="24" t="n"/>
+      <c r="DI53" s="24" t="n"/>
+      <c r="DJ53" s="24" t="n"/>
+      <c r="DK53" s="24" t="n"/>
+      <c r="DL53" s="24" t="n"/>
+      <c r="DM53" s="24" t="n"/>
+      <c r="DN53" s="24" t="n"/>
+      <c r="DO53" s="24" t="n"/>
+      <c r="DP53" s="24" t="n"/>
+      <c r="DQ53" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "6ba5d15b40a8ae0fc6edef9d2ee0f3d04150e80e420234231fec1c3c345f7a8f", "away_team": "100 Thieves", "event_id": "144060", "event_start_utc": "2026-10-08T18:00:00Z", "features": {"away_elo": 1610.34644, "away_history_count": 24, "home_elo": 1700.940012, "home_history_count": 89}, "historical_source_observation_times_verified": false, "home_team": "Shopify Rebellion", "inference_inputs": {"book_state": {"games_played": {"bo3:7:19762": 89, "bo3:7:23109": 24}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 32.0, "last_match_utc": {"bo3:7:19762": "2026-10-02T19:00:00Z", "bo3:7:23109": "2026-10-02T21:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.1361313041024407, "platt_slope": 0.7681778963758318, "ratings": {"bo3:7:19762": 1700.940012, "bo3:7:23109": 1610.34644}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T22:27:21.600823+00:00", "team_ids": ["bo3:7:19762", "bo3:7:23109"]}, "market_type": "moneyline", "model_version": "rainbow_six-tiered-elo-v6", "observed_at_utc": "2026-10-07T22:27:21.600823+00:00", "probabilities": {"away": 0.391968, "home": 0.608032}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "12151b65c9d7281343a596a8b118e9d9220cf53d98715a002183be6125f79152", "sport": "RAINBOW_SIX"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>eba8f49a255e4a5c</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:28:03.287087Z</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>144618</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>RAINBOW_SIX</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="H54" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L54" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M54" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N54" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O54" s="28" t="n">
+        <v>0.557868</v>
+      </c>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="28" t="n">
+        <v>0.097039</v>
+      </c>
+      <c r="R54" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S54" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T54" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U54" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V54" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W54" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="25" t="n"/>
+      <c r="Z54" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA54" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB54" s="28" t="n">
+        <v>0.109171</v>
+      </c>
+      <c r="AC54" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD54" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:37:14.178180Z</t>
+        </is>
+      </c>
+      <c r="AE54" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-r6-furia-liquid-2026-10-09).</t>
+        </is>
+      </c>
+      <c r="AF54" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG54" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH54" s="24" t="n"/>
+      <c r="AI54" s="31" t="n"/>
+      <c r="AJ54" s="31" t="n"/>
+      <c r="AK54" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL54" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM54" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN54" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO54" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP54" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="AQ54" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="AR54" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="AS54" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AT54" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AU54" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AV54" s="24" t="n"/>
+      <c r="AW54" s="24" t="n"/>
+      <c r="AX54" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY54" s="24" t="n"/>
+      <c r="AZ54" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA54" s="24" t="inlineStr">
+        <is>
+          <t>6ba5d15b40a8ae0fc6edef9d2ee0f3d04150e80e420234231fec1c3c345f7a8f</t>
+        </is>
+      </c>
+      <c r="BB54" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC54" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD54" s="24" t="inlineStr">
+        <is>
+          <t>6ba5d15b40a8ae0fc6edef9d2ee0f3d04150e80e420234231fec1c3c345f7a8f</t>
+        </is>
+      </c>
+      <c r="BE54" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF54" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG54" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH54" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:28:02.878689Z</t>
+        </is>
+      </c>
+      <c r="BI54" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ54" s="25" t="n"/>
+      <c r="BK54" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL54" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM54" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN54" s="28" t="n"/>
+      <c r="BO54" s="28" t="n"/>
+      <c r="BP54" s="25" t="n"/>
+      <c r="BQ54" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR54" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BS54" s="28" t="n"/>
+      <c r="BT54" s="28" t="n"/>
+      <c r="BU54" s="25" t="n"/>
+      <c r="BV54" s="29" t="n"/>
+      <c r="BW54" s="24" t="n"/>
+      <c r="BX54" s="30" t="n"/>
+      <c r="BY54" s="27" t="n"/>
+      <c r="BZ54" s="24" t="n"/>
+      <c r="CA54" s="31" t="n"/>
+      <c r="CB54" s="24" t="n"/>
+      <c r="CC54" s="24" t="n"/>
+      <c r="CD54" s="24" t="n"/>
+      <c r="CE54" s="24" t="n"/>
+      <c r="CF54" s="24" t="n"/>
+      <c r="CG54" s="24" t="n"/>
+      <c r="CH54" s="24" t="n"/>
+      <c r="CI54" s="24" t="n"/>
+      <c r="CJ54" s="24" t="n"/>
+      <c r="CK54" s="24" t="n"/>
+      <c r="CL54" s="24" t="n"/>
+      <c r="CM54" s="24" t="n"/>
+      <c r="CN54" s="24" t="n"/>
+      <c r="CO54" s="24" t="n"/>
+      <c r="CP54" s="24" t="n"/>
+      <c r="CQ54" s="24" t="n"/>
+      <c r="CR54" s="24" t="n"/>
+      <c r="CS54" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT54" s="24" t="n"/>
+      <c r="CU54" s="24" t="n"/>
+      <c r="CV54" s="24" t="n"/>
+      <c r="CW54" s="24" t="n"/>
+      <c r="CX54" s="24" t="n"/>
+      <c r="CY54" s="24" t="n"/>
+      <c r="CZ54" s="24" t="n"/>
+      <c r="DA54" s="24" t="n"/>
+      <c r="DB54" s="24" t="n"/>
+      <c r="DC54" s="24" t="n"/>
+      <c r="DD54" s="24" t="n"/>
+      <c r="DE54" s="24" t="n"/>
+      <c r="DF54" s="24" t="n"/>
+      <c r="DG54" s="24" t="n"/>
+      <c r="DH54" s="24" t="n"/>
+      <c r="DI54" s="24" t="n"/>
+      <c r="DJ54" s="24" t="n"/>
+      <c r="DK54" s="24" t="n"/>
+      <c r="DL54" s="24" t="n"/>
+      <c r="DM54" s="24" t="n"/>
+      <c r="DN54" s="24" t="n"/>
+      <c r="DO54" s="24" t="n"/>
+      <c r="DP54" s="24" t="n"/>
+      <c r="DQ54" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "6ba5d15b40a8ae0fc6edef9d2ee0f3d04150e80e420234231fec1c3c345f7a8f", "away_team": "Team Liquid", "event_id": "144618", "event_start_utc": "2026-10-09T00:00:00Z", "features": {"away_elo": 1730.301619, "away_history_count": 123, "home_elo": 1762.2002, "home_history_count": 143}, "historical_source_observation_times_verified": false, "home_team": "FURIA Esports", "inference_inputs": {"book_state": {"games_played": {"bo3:7:19662": 143, "bo3:7:19720": 123}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 32.0, "last_match_utc": {"bo3:7:19662": "2026-10-04T21:20:00Z", "bo3:7:19720": "2026-10-04T18:30:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.1361313041024407, "platt_slope": 0.7681778963758318, "ratings": {"bo3:7:19662": 1762.2002, "bo3:7:19720": 1730.301619}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T22:27:21.600823+00:00", "team_ids": ["bo3:7:19662", "bo3:7:19720"]}, "market_type": "moneyline", "model_version": "rainbow_six-tiered-elo-v6", "observed_at_utc": "2026-10-07T22:27:21.600823+00:00", "probabilities": {"away": 0.442132, "home": 0.557868}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "1227f5cf0efa572e4ec9d2eb26e9cfc8000f97349404efb4207d35b3bab65590", "sport": "RAINBOW_SIX"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>c06f5a7c802a4893</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T11:04:15.044727Z</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>151232</t>
+        </is>
+      </c>
+      <c r="E55" s="24" t="inlineStr">
+        <is>
+          <t>RAINBOW_SIX</t>
+        </is>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t>Falcons Esport</t>
+        </is>
+      </c>
+      <c r="H55" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I55" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J55" s="25" t="n"/>
+      <c r="K55" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L55" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M55" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N55" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O55" s="28" t="n">
+        <v>0.503418</v>
+      </c>
+      <c r="P55" s="28" t="n"/>
+      <c r="Q55" s="28" t="n">
+        <v>-0.015813</v>
+      </c>
+      <c r="R55" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="S55" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U55" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V55" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" s="25" t="n"/>
+      <c r="Z55" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="AA55" s="28" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB55" s="28" t="n">
+        <v>0.000769</v>
+      </c>
+      <c r="AC55" s="30" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="AD55" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T22:03:33.550642Z</t>
+        </is>
+      </c>
+      <c r="AE55" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-r6-flcs-g2-2026-10-12).</t>
+        </is>
+      </c>
+      <c r="AF55" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG55" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH55" s="24" t="n"/>
+      <c r="AI55" s="31" t="n"/>
+      <c r="AJ55" s="31" t="n"/>
+      <c r="AK55" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL55" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM55" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN55" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO55" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP55" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AQ55" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AR55" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AS55" s="24" t="inlineStr">
+        <is>
+          <t>Falcons Esport</t>
+        </is>
+      </c>
+      <c r="AT55" s="24" t="inlineStr">
+        <is>
+          <t>Falcons Esport</t>
+        </is>
+      </c>
+      <c r="AU55" s="24" t="inlineStr">
+        <is>
+          <t>Falcons Esport</t>
+        </is>
+      </c>
+      <c r="AV55" s="24" t="n"/>
+      <c r="AW55" s="24" t="n"/>
+      <c r="AX55" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY55" s="24" t="n"/>
+      <c r="AZ55" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA55" s="24" t="inlineStr">
+        <is>
+          <t>2d38e60d3b7e4a6bcc7eb232756e397e4733295e854167b83389c8d46c85fe60</t>
+        </is>
+      </c>
+      <c r="BB55" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC55" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD55" s="24" t="inlineStr">
+        <is>
+          <t>2d38e60d3b7e4a6bcc7eb232756e397e4733295e854167b83389c8d46c85fe60</t>
+        </is>
+      </c>
+      <c r="BE55" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF55" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG55" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH55" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T11:03:23.993111Z</t>
+        </is>
+      </c>
+      <c r="BI55" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ55" s="25" t="n"/>
+      <c r="BK55" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL55" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM55" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN55" s="28" t="n"/>
+      <c r="BO55" s="28" t="n"/>
+      <c r="BP55" s="25" t="n"/>
+      <c r="BQ55" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BR55" s="28" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BS55" s="28" t="n"/>
+      <c r="BT55" s="28" t="n"/>
+      <c r="BU55" s="25" t="n"/>
+      <c r="BV55" s="29" t="n"/>
+      <c r="BW55" s="24" t="n"/>
+      <c r="BX55" s="30" t="n"/>
+      <c r="BY55" s="27" t="n"/>
+      <c r="BZ55" s="24" t="n"/>
+      <c r="CA55" s="31" t="n"/>
+      <c r="CB55" s="24" t="n"/>
+      <c r="CC55" s="24" t="n"/>
+      <c r="CD55" s="24" t="n"/>
+      <c r="CE55" s="24" t="n"/>
+      <c r="CF55" s="24" t="n"/>
+      <c r="CG55" s="24" t="n"/>
+      <c r="CH55" s="24" t="n"/>
+      <c r="CI55" s="24" t="n"/>
+      <c r="CJ55" s="24" t="n"/>
+      <c r="CK55" s="24" t="n"/>
+      <c r="CL55" s="24" t="n"/>
+      <c r="CM55" s="24" t="n"/>
+      <c r="CN55" s="24" t="n"/>
+      <c r="CO55" s="24" t="n"/>
+      <c r="CP55" s="24" t="n"/>
+      <c r="CQ55" s="24" t="n"/>
+      <c r="CR55" s="24" t="n"/>
+      <c r="CS55" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT55" s="24" t="n"/>
+      <c r="CU55" s="24" t="n"/>
+      <c r="CV55" s="24" t="n"/>
+      <c r="CW55" s="24" t="n"/>
+      <c r="CX55" s="24" t="n"/>
+      <c r="CY55" s="24" t="n"/>
+      <c r="CZ55" s="24" t="n"/>
+      <c r="DA55" s="24" t="n"/>
+      <c r="DB55" s="24" t="n"/>
+      <c r="DC55" s="24" t="n"/>
+      <c r="DD55" s="24" t="n"/>
+      <c r="DE55" s="24" t="n"/>
+      <c r="DF55" s="24" t="n"/>
+      <c r="DG55" s="24" t="n"/>
+      <c r="DH55" s="24" t="n"/>
+      <c r="DI55" s="24" t="n"/>
+      <c r="DJ55" s="24" t="n"/>
+      <c r="DK55" s="24" t="n"/>
+      <c r="DL55" s="24" t="n"/>
+      <c r="DM55" s="24" t="n"/>
+      <c r="DN55" s="24" t="n"/>
+      <c r="DO55" s="24" t="n"/>
+      <c r="DP55" s="24" t="n"/>
+      <c r="DQ55" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "2d38e60d3b7e4a6bcc7eb232756e397e4733295e854167b83389c8d46c85fe60", "away_team": "G2 Esports", "event_id": "151232", "event_start_utc": "2026-10-12T16:00:00Z", "features": {"away_elo": 1816.240593, "away_history_count": 149, "home_elo": 1787.811904, "home_history_count": 128}, "historical_source_observation_times_verified": false, "home_team": "Falcons Esport", "inference_inputs": {"book_state": {"games_played": {"bo3:7:19439": 128, "bo3:7:19715": 149}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 32.0, "last_match_utc": {"bo3:7:19439": "2026-10-05T16:00:00Z", "bo3:7:19715": "2026-10-05T18:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.13189564392408787, "platt_slope": 0.7456028563944902, "ratings": {"bo3:7:19439": 1787.811904, "bo3:7:19715": 1816.240593}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-12T11:03:23.889273+00:00", "team_ids": ["bo3:7:19439", "bo3:7:19715"]}, "market_type": "moneyline", "model_version": "rainbow_six-tiered-elo-v6", "observed_at_utc": "2026-10-12T11:03:23.889273+00:00", "probabilities": {"away": 0.496582, "home": 0.503418}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "1be75c5bd1b181145c51a09b0431f75803773fbc31e536055b6faef62f490ca1", "sport": "RAINBOW_SIX"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>6a9827ae055b43ba</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T16:51:50.855971Z</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>151517</t>
+        </is>
+      </c>
+      <c r="E56" s="24" t="inlineStr">
+        <is>
+          <t>RAINBOW_SIX</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>Virtus.pro</t>
+        </is>
+      </c>
+      <c r="G56" s="24" t="inlineStr">
+        <is>
+          <t>Geekay Esports</t>
+        </is>
+      </c>
+      <c r="H56" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I56" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J56" s="25" t="n"/>
+      <c r="K56" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L56" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M56" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N56" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O56" s="28" t="n">
+        <v>0.509543</v>
+      </c>
+      <c r="P56" s="28" t="n"/>
+      <c r="Q56" s="28" t="n">
+        <v>-0.160424</v>
+      </c>
+      <c r="R56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U56" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V56" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="25" t="n"/>
+      <c r="Z56" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="AA56" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB56" s="28" t="n">
+        <v>3.3e-05</v>
+      </c>
+      <c r="AC56" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD56" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T22:03:35.098740Z</t>
+        </is>
+      </c>
+      <c r="AE56" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-r6-ge-vp-2026-10-12).</t>
+        </is>
+      </c>
+      <c r="AF56" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG56" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH56" s="24" t="n"/>
+      <c r="AI56" s="31" t="n"/>
+      <c r="AJ56" s="31" t="n"/>
+      <c r="AK56" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL56" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM56" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN56" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO56" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP56" s="24" t="inlineStr">
+        <is>
+          <t>Virtus.pro</t>
+        </is>
+      </c>
+      <c r="AQ56" s="24" t="inlineStr">
+        <is>
+          <t>Virtus.pro</t>
+        </is>
+      </c>
+      <c r="AR56" s="24" t="inlineStr">
+        <is>
+          <t>Virtus.pro</t>
+        </is>
+      </c>
+      <c r="AS56" s="24" t="inlineStr">
+        <is>
+          <t>Geekay Esports</t>
+        </is>
+      </c>
+      <c r="AT56" s="24" t="inlineStr">
+        <is>
+          <t>Geekay Esports</t>
+        </is>
+      </c>
+      <c r="AU56" s="24" t="inlineStr">
+        <is>
+          <t>Geekay Esports</t>
+        </is>
+      </c>
+      <c r="AV56" s="24" t="n"/>
+      <c r="AW56" s="24" t="n"/>
+      <c r="AX56" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY56" s="24" t="n"/>
+      <c r="AZ56" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA56" s="24" t="inlineStr">
+        <is>
+          <t>152f414c029b2d0fa2242f6737b546bf9a05fb8276bb911c2169b65002542354</t>
+        </is>
+      </c>
+      <c r="BB56" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC56" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD56" s="24" t="inlineStr">
+        <is>
+          <t>152f414c029b2d0fa2242f6737b546bf9a05fb8276bb911c2169b65002542354</t>
+        </is>
+      </c>
+      <c r="BE56" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF56" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG56" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH56" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T16:51:27.147501Z</t>
+        </is>
+      </c>
+      <c r="BI56" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ56" s="25" t="n"/>
+      <c r="BK56" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL56" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM56" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN56" s="28" t="n"/>
+      <c r="BO56" s="28" t="n"/>
+      <c r="BP56" s="25" t="n"/>
+      <c r="BQ56" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BR56" s="28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BS56" s="28" t="n"/>
+      <c r="BT56" s="28" t="n"/>
+      <c r="BU56" s="25" t="n"/>
+      <c r="BV56" s="29" t="n"/>
+      <c r="BW56" s="24" t="n"/>
+      <c r="BX56" s="30" t="n"/>
+      <c r="BY56" s="27" t="n"/>
+      <c r="BZ56" s="24" t="n"/>
+      <c r="CA56" s="31" t="n"/>
+      <c r="CB56" s="24" t="n"/>
+      <c r="CC56" s="24" t="n"/>
+      <c r="CD56" s="24" t="n"/>
+      <c r="CE56" s="24" t="n"/>
+      <c r="CF56" s="24" t="n"/>
+      <c r="CG56" s="24" t="n"/>
+      <c r="CH56" s="24" t="n"/>
+      <c r="CI56" s="24" t="n"/>
+      <c r="CJ56" s="24" t="n"/>
+      <c r="CK56" s="24" t="n"/>
+      <c r="CL56" s="24" t="n"/>
+      <c r="CM56" s="24" t="n"/>
+      <c r="CN56" s="24" t="n"/>
+      <c r="CO56" s="24" t="n"/>
+      <c r="CP56" s="24" t="n"/>
+      <c r="CQ56" s="24" t="n"/>
+      <c r="CR56" s="24" t="n"/>
+      <c r="CS56" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT56" s="24" t="n"/>
+      <c r="CU56" s="24" t="n"/>
+      <c r="CV56" s="24" t="n"/>
+      <c r="CW56" s="24" t="n"/>
+      <c r="CX56" s="24" t="n"/>
+      <c r="CY56" s="24" t="n"/>
+      <c r="CZ56" s="24" t="n"/>
+      <c r="DA56" s="24" t="n"/>
+      <c r="DB56" s="24" t="n"/>
+      <c r="DC56" s="24" t="n"/>
+      <c r="DD56" s="24" t="n"/>
+      <c r="DE56" s="24" t="n"/>
+      <c r="DF56" s="24" t="n"/>
+      <c r="DG56" s="24" t="n"/>
+      <c r="DH56" s="24" t="n"/>
+      <c r="DI56" s="24" t="n"/>
+      <c r="DJ56" s="24" t="n"/>
+      <c r="DK56" s="24" t="n"/>
+      <c r="DL56" s="24" t="n"/>
+      <c r="DM56" s="24" t="n"/>
+      <c r="DN56" s="24" t="n"/>
+      <c r="DO56" s="24" t="n"/>
+      <c r="DP56" s="24" t="n"/>
+      <c r="DQ56" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "152f414c029b2d0fa2242f6737b546bf9a05fb8276bb911c2169b65002542354", "away_team": "Virtus.pro", "event_id": "151517", "event_start_utc": "2026-10-12T19:00:00Z", "features": {"away_elo": 1702.410364, "away_history_count": 113, "home_elo": 1659.108757, "home_history_count": 62}, "historical_source_observation_times_verified": false, "home_team": "Geekay Esports", "inference_inputs": {"book_state": {"games_played": {"bo3:7:19340": 62, "bo3:7:19668": 113}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 32.0, "last_match_utc": {"bo3:7:19340": "2026-10-06T16:00:00Z", "bo3:7:19668": "2026-10-06T19:15:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.13189564392408787, "platt_slope": 0.7456028563944902, "ratings": {"bo3:7:19340": 1659.108757, "bo3:7:19668": 1702.410364}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-12T16:51:27.018707+00:00", "team_ids": ["bo3:7:19340", "bo3:7:19668"]}, "market_type": "moneyline", "model_version": "rainbow_six-tiered-elo-v6", "observed_at_utc": "2026-10-12T16:51:27.018707+00:00", "probabilities": {"away": 0.509543, "home": 0.490457}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "390aced1da1eecb9f19307e3871f933ec6dced38f6366c1223b22e5d86ae431b", "sport": "RAINBOW_SIX"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/sports/rainbow_six/research.xlsx
+++ b/data/sports/rainbow_six/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ56" headerRowCount="1">
-  <autoFilter ref="A1:DQ56"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ58" headerRowCount="1">
+  <autoFilter ref="A1:DQ58"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$56)</f>
+        <f>COUNTA('Picks'!$A$2:$A$58)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$56,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$58,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$56,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$58,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"win")+COUNTIFS('Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$58,"settled",'Picks'!$V$2:$V$58,"win")+COUNTIFS('Picks'!$U$2:$U$58,"settled",'Picks'!$V$2:$V$58,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$56,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$58,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$56,"&gt;0",'Picks'!$V$2:$V$56,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$56,"&gt;0",'Picks'!$V$2:$V$56,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$58,"&gt;0",'Picks'!$V$2:$V$58,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$58,"&gt;0",'Picks'!$V$2:$V$58,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$56,"&gt;0",'Picks'!$V$2:$V$56,"win")/(COUNTIFS('Picks'!$BX$2:$BX$56,"&gt;0",'Picks'!$V$2:$V$56,"win")+COUNTIFS('Picks'!$BX$2:$BX$56,"&gt;0",'Picks'!$V$2:$V$56,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$58,"&gt;0",'Picks'!$V$2:$V$58,"win")/(COUNTIFS('Picks'!$BX$2:$BX$58,"&gt;0",'Picks'!$V$2:$V$58,"win")+COUNTIFS('Picks'!$BX$2:$BX$58,"&gt;0",'Picks'!$V$2:$V$58,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$56)/SUM('Picks'!$BX$2:$BX$56),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$58)/SUM('Picks'!$BX$2:$BX$58),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$56)</f>
+        <f>SUM('Picks'!$BY$2:$BY$58)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$56,"&lt;&gt;",'Picks'!$AB$2:$AB$56),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$58,"&lt;&gt;",'Picks'!$AB$2:$AB$58),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$56,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$56,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$58,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$58,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$56,'Picks'!$AM$2:$AM$56,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$58,'Picks'!$AM$2:$AM$58,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$56,$A14,'Picks'!$U$2:$U$56,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$58,$A14,'Picks'!$U$2:$U$58,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$56,$A14,'Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$58,$A14,'Picks'!$U$2:$U$58,"settled",'Picks'!$V$2:$V$58,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$56,$A14,'Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$58,$A14,'Picks'!$U$2:$U$58,"settled",'Picks'!$V$2:$V$58,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$56,'Picks'!$H$2:$H$56,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$58,'Picks'!$H$2:$H$58,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$56,'Picks'!$H$2:$H$56,$A14,'Picks'!$U$2:$U$56,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$58,'Picks'!$H$2:$H$58,$A14,'Picks'!$U$2:$U$58,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$56,$A15,'Picks'!$U$2:$U$56,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$58,$A15,'Picks'!$U$2:$U$58,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$56,$A15,'Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$58,$A15,'Picks'!$U$2:$U$58,"settled",'Picks'!$V$2:$V$58,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$56,$A15,'Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$58,$A15,'Picks'!$U$2:$U$58,"settled",'Picks'!$V$2:$V$58,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$56,'Picks'!$H$2:$H$56,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$58,'Picks'!$H$2:$H$58,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$56,'Picks'!$H$2:$H$56,$A15,'Picks'!$U$2:$U$56,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$58,'Picks'!$H$2:$H$58,$A15,'Picks'!$U$2:$U$58,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$56,$A16,'Picks'!$U$2:$U$56,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$58,$A16,'Picks'!$U$2:$U$58,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$56,$A16,'Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$58,$A16,'Picks'!$U$2:$U$58,"settled",'Picks'!$V$2:$V$58,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$56,$A16,'Picks'!$U$2:$U$56,"settled",'Picks'!$V$2:$V$56,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$58,$A16,'Picks'!$U$2:$U$58,"settled",'Picks'!$V$2:$V$58,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$56,'Picks'!$H$2:$H$56,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$58,'Picks'!$H$2:$H$58,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$56,'Picks'!$H$2:$H$56,$A16,'Picks'!$U$2:$U$56,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$58,'Picks'!$H$2:$H$58,$A16,'Picks'!$U$2:$U$58,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ56"/>
+  <dimension ref="A1:DQ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19372,6 +19372,600 @@
         </is>
       </c>
     </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>5bb6fb773f13422d</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:47:02.924500Z</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>156920</t>
+        </is>
+      </c>
+      <c r="E57" s="24" t="inlineStr">
+        <is>
+          <t>RAINBOW_SIX</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>DarkZero Esports</t>
+        </is>
+      </c>
+      <c r="H57" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I57" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J57" s="25" t="n"/>
+      <c r="K57" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L57" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M57" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N57" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O57" s="28" t="n">
+        <v>0.566617</v>
+      </c>
+      <c r="P57" s="28" t="n"/>
+      <c r="Q57" s="28" t="n">
+        <v>0.007146</v>
+      </c>
+      <c r="R57" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="S57" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U57" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V57" s="24" t="n"/>
+      <c r="W57" s="26" t="n"/>
+      <c r="X57" s="26" t="n"/>
+      <c r="Y57" s="25" t="n"/>
+      <c r="Z57" s="26" t="n"/>
+      <c r="AA57" s="28" t="n"/>
+      <c r="AB57" s="28" t="n"/>
+      <c r="AC57" s="30" t="n"/>
+      <c r="AD57" s="24" t="n"/>
+      <c r="AE57" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-r6-dz-m80-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF57" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG57" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH57" s="24" t="n"/>
+      <c r="AI57" s="31" t="n"/>
+      <c r="AJ57" s="31" t="n"/>
+      <c r="AK57" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL57" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM57" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN57" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO57" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP57" s="24" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="AQ57" s="24" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="AR57" s="24" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="AS57" s="24" t="inlineStr">
+        <is>
+          <t>DarkZero Esports</t>
+        </is>
+      </c>
+      <c r="AT57" s="24" t="inlineStr">
+        <is>
+          <t>DarkZero Esports</t>
+        </is>
+      </c>
+      <c r="AU57" s="24" t="inlineStr">
+        <is>
+          <t>DarkZero Esports</t>
+        </is>
+      </c>
+      <c r="AV57" s="24" t="n"/>
+      <c r="AW57" s="24" t="n"/>
+      <c r="AX57" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY57" s="24" t="n"/>
+      <c r="AZ57" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA57" s="24" t="inlineStr">
+        <is>
+          <t>a0e7aadedfb080b338b630ad79e8d3ce2d8fe02cb84073a39c157b641c45454b</t>
+        </is>
+      </c>
+      <c r="BB57" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC57" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD57" s="24" t="inlineStr">
+        <is>
+          <t>a0e7aadedfb080b338b630ad79e8d3ce2d8fe02cb84073a39c157b641c45454b</t>
+        </is>
+      </c>
+      <c r="BE57" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF57" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG57" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH57" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:32.880591Z</t>
+        </is>
+      </c>
+      <c r="BI57" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ57" s="25" t="n"/>
+      <c r="BK57" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL57" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM57" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN57" s="28" t="n"/>
+      <c r="BO57" s="28" t="n"/>
+      <c r="BP57" s="25" t="n"/>
+      <c r="BQ57" s="27" t="n"/>
+      <c r="BR57" s="28" t="n"/>
+      <c r="BS57" s="28" t="n"/>
+      <c r="BT57" s="28" t="n"/>
+      <c r="BU57" s="25" t="n"/>
+      <c r="BV57" s="29" t="n"/>
+      <c r="BW57" s="24" t="n"/>
+      <c r="BX57" s="30" t="n"/>
+      <c r="BY57" s="27" t="n"/>
+      <c r="BZ57" s="24" t="n"/>
+      <c r="CA57" s="31" t="n"/>
+      <c r="CB57" s="24" t="n"/>
+      <c r="CC57" s="24" t="n"/>
+      <c r="CD57" s="24" t="n"/>
+      <c r="CE57" s="24" t="n"/>
+      <c r="CF57" s="24" t="n"/>
+      <c r="CG57" s="24" t="n"/>
+      <c r="CH57" s="24" t="n"/>
+      <c r="CI57" s="24" t="n"/>
+      <c r="CJ57" s="24" t="n"/>
+      <c r="CK57" s="24" t="n"/>
+      <c r="CL57" s="24" t="n"/>
+      <c r="CM57" s="24" t="n"/>
+      <c r="CN57" s="24" t="n"/>
+      <c r="CO57" s="24" t="n"/>
+      <c r="CP57" s="24" t="n"/>
+      <c r="CQ57" s="24" t="n"/>
+      <c r="CR57" s="24" t="n"/>
+      <c r="CS57" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT57" s="24" t="n"/>
+      <c r="CU57" s="24" t="n"/>
+      <c r="CV57" s="24" t="n"/>
+      <c r="CW57" s="24" t="n"/>
+      <c r="CX57" s="24" t="n"/>
+      <c r="CY57" s="24" t="n"/>
+      <c r="CZ57" s="24" t="n"/>
+      <c r="DA57" s="24" t="n"/>
+      <c r="DB57" s="24" t="n"/>
+      <c r="DC57" s="24" t="n"/>
+      <c r="DD57" s="24" t="n"/>
+      <c r="DE57" s="24" t="n"/>
+      <c r="DF57" s="24" t="n"/>
+      <c r="DG57" s="24" t="n"/>
+      <c r="DH57" s="24" t="n"/>
+      <c r="DI57" s="24" t="n"/>
+      <c r="DJ57" s="24" t="n"/>
+      <c r="DK57" s="24" t="n"/>
+      <c r="DL57" s="24" t="n"/>
+      <c r="DM57" s="24" t="n"/>
+      <c r="DN57" s="24" t="n"/>
+      <c r="DO57" s="24" t="n"/>
+      <c r="DP57" s="24" t="n"/>
+      <c r="DQ57" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "a0e7aadedfb080b338b630ad79e8d3ce2d8fe02cb84073a39c157b641c45454b", "away_team": "M80", "event_id": "156920", "event_start_utc": "2026-10-15T18:00:00Z", "features": {"away_elo": 1678.164938, "away_history_count": 121, "home_elo": 1723.389485, "home_history_count": 129}, "historical_source_observation_times_verified": false, "home_team": "DarkZero Esports", "inference_inputs": {"book_state": {"games_played": {"bo3:7:19363": 121, "bo3:7:19729": 129}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 32.0, "last_match_utc": {"bo3:7:19363": "2026-10-09T18:00:00Z", "bo3:7:19729": "2026-10-09T15:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.13453246480031117, "platt_slope": 0.7361238041647814, "ratings": {"bo3:7:19363": 1678.164938, "bo3:7:19729": 1723.389485}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.767061+00:00", "team_ids": ["bo3:7:19729", "bo3:7:19363"]}, "market_type": "moneyline", "model_version": "rainbow_six-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.767061+00:00", "probabilities": {"away": 0.433383, "home": 0.566617}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "fde7b9b77d9f0cac63b1324a0c84107a973fb7b2a161b3aaa85e1005f87d91df", "sport": "RAINBOW_SIX"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>4e97234fd32a4427</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:47:02.924500Z</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>157366</t>
+        </is>
+      </c>
+      <c r="E58" s="24" t="inlineStr">
+        <is>
+          <t>RAINBOW_SIX</t>
+        </is>
+      </c>
+      <c r="F58" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="G58" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="H58" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I58" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J58" s="25" t="n"/>
+      <c r="K58" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L58" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M58" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N58" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O58" s="28" t="n">
+        <v>0.5473209999999999</v>
+      </c>
+      <c r="P58" s="28" t="n"/>
+      <c r="Q58" s="28" t="n">
+        <v>0.02809</v>
+      </c>
+      <c r="R58" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="S58" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U58" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V58" s="24" t="n"/>
+      <c r="W58" s="26" t="n"/>
+      <c r="X58" s="26" t="n"/>
+      <c r="Y58" s="25" t="n"/>
+      <c r="Z58" s="26" t="n"/>
+      <c r="AA58" s="28" t="n"/>
+      <c r="AB58" s="28" t="n"/>
+      <c r="AC58" s="30" t="n"/>
+      <c r="AD58" s="24" t="n"/>
+      <c r="AE58" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-r6-c9-100t-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF58" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG58" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH58" s="24" t="n"/>
+      <c r="AI58" s="31" t="n"/>
+      <c r="AJ58" s="31" t="n"/>
+      <c r="AK58" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL58" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM58" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN58" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO58" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP58" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AQ58" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AR58" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AS58" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AT58" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AU58" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AV58" s="24" t="n"/>
+      <c r="AW58" s="24" t="n"/>
+      <c r="AX58" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY58" s="24" t="n"/>
+      <c r="AZ58" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA58" s="24" t="inlineStr">
+        <is>
+          <t>a0e7aadedfb080b338b630ad79e8d3ce2d8fe02cb84073a39c157b641c45454b</t>
+        </is>
+      </c>
+      <c r="BB58" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC58" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD58" s="24" t="inlineStr">
+        <is>
+          <t>a0e7aadedfb080b338b630ad79e8d3ce2d8fe02cb84073a39c157b641c45454b</t>
+        </is>
+      </c>
+      <c r="BE58" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF58" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG58" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH58" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:47:02.905029Z</t>
+        </is>
+      </c>
+      <c r="BI58" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ58" s="25" t="n"/>
+      <c r="BK58" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL58" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM58" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN58" s="28" t="n"/>
+      <c r="BO58" s="28" t="n"/>
+      <c r="BP58" s="25" t="n"/>
+      <c r="BQ58" s="27" t="n"/>
+      <c r="BR58" s="28" t="n"/>
+      <c r="BS58" s="28" t="n"/>
+      <c r="BT58" s="28" t="n"/>
+      <c r="BU58" s="25" t="n"/>
+      <c r="BV58" s="29" t="n"/>
+      <c r="BW58" s="24" t="n"/>
+      <c r="BX58" s="30" t="n"/>
+      <c r="BY58" s="27" t="n"/>
+      <c r="BZ58" s="24" t="n"/>
+      <c r="CA58" s="31" t="n"/>
+      <c r="CB58" s="24" t="n"/>
+      <c r="CC58" s="24" t="n"/>
+      <c r="CD58" s="24" t="n"/>
+      <c r="CE58" s="24" t="n"/>
+      <c r="CF58" s="24" t="n"/>
+      <c r="CG58" s="24" t="n"/>
+      <c r="CH58" s="24" t="n"/>
+      <c r="CI58" s="24" t="n"/>
+      <c r="CJ58" s="24" t="n"/>
+      <c r="CK58" s="24" t="n"/>
+      <c r="CL58" s="24" t="n"/>
+      <c r="CM58" s="24" t="n"/>
+      <c r="CN58" s="24" t="n"/>
+      <c r="CO58" s="24" t="n"/>
+      <c r="CP58" s="24" t="n"/>
+      <c r="CQ58" s="24" t="n"/>
+      <c r="CR58" s="24" t="n"/>
+      <c r="CS58" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT58" s="24" t="n"/>
+      <c r="CU58" s="24" t="n"/>
+      <c r="CV58" s="24" t="n"/>
+      <c r="CW58" s="24" t="n"/>
+      <c r="CX58" s="24" t="n"/>
+      <c r="CY58" s="24" t="n"/>
+      <c r="CZ58" s="24" t="n"/>
+      <c r="DA58" s="24" t="n"/>
+      <c r="DB58" s="24" t="n"/>
+      <c r="DC58" s="24" t="n"/>
+      <c r="DD58" s="24" t="n"/>
+      <c r="DE58" s="24" t="n"/>
+      <c r="DF58" s="24" t="n"/>
+      <c r="DG58" s="24" t="n"/>
+      <c r="DH58" s="24" t="n"/>
+      <c r="DI58" s="24" t="n"/>
+      <c r="DJ58" s="24" t="n"/>
+      <c r="DK58" s="24" t="n"/>
+      <c r="DL58" s="24" t="n"/>
+      <c r="DM58" s="24" t="n"/>
+      <c r="DN58" s="24" t="n"/>
+      <c r="DO58" s="24" t="n"/>
+      <c r="DP58" s="24" t="n"/>
+      <c r="DQ58" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "a0e7aadedfb080b338b630ad79e8d3ce2d8fe02cb84073a39c157b641c45454b", "away_team": "100 Thieves", "event_id": "157366", "event_start_utc": "2026-10-15T21:00:00Z", "features": {"away_elo": 1636.682624, "away_history_count": 25, "home_elo": 1659.199516, "home_history_count": 53}, "historical_source_observation_times_verified": false, "home_team": "Cloud9", "inference_inputs": {"book_state": {"games_played": {"bo3:7:19685": 53, "bo3:7:23109": 25}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 32.0, "last_match_utc": {"bo3:7:19685": "2026-10-08T15:00:00Z", "bo3:7:23109": "2026-10-08T18:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.13453246480031117, "platt_slope": 0.7361238041647814, "ratings": {"bo3:7:19685": 1659.199516, "bo3:7:23109": 1636.682624}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.767061+00:00", "team_ids": ["bo3:7:19685", "bo3:7:23109"]}, "market_type": "moneyline", "model_version": "rainbow_six-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.767061+00:00", "probabilities": {"away": 0.452679, "home": 0.547321}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "5291f40ca5718d32638f81de267588cfce199a98e01e7fcfa5dab1b6eeae918a", "sport": "RAINBOW_SIX"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
